--- a/site/downloads/tx-ag-wildlife-valuation-checklist.xlsx
+++ b/site/downloads/tx-ag-wildlife-valuation-checklist.xlsx
@@ -569,7 +569,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Built by Lone Star Exotics Hub (draft), Oct 2026. Verify every figure against the current publication; tax law changes.</t>
+          <t>Built by Exotic Ranch &amp; Wildlife Network (draft), Oct 2026. Verify every figure against the current publication; tax law changes.</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,6 @@
           <t>A. GENERAL</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -660,7 +659,6 @@
         </is>
       </c>
       <c r="B6" s="7" t="n"/>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -681,7 +679,6 @@
           <t>B. EXOTIC LIVESTOCK (1-d-1) PATH</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -728,7 +725,6 @@
           <t>C. WILDLIFE MANAGEMENT PATH (native species only)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
